--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484605_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484605_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.609299999999999</v>
+        <v>9.505100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.494</v>
+        <v>5.5385</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1153</v>
+        <v>3.9666</v>
       </c>
       <c r="G2" t="n">
         <v>7.9368</v>
@@ -610,13 +610,13 @@
         <v>2.9321</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5554</v>
+        <v>0.3405</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8627</v>
+        <v>0.1818</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3074</v>
+        <v>0.1587</v>
       </c>
       <c r="V2" t="n">
         <v>0.3115</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2245</v>
+        <v>7.1428</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8112</v>
+        <v>6.6057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4133</v>
+        <v>0.5372</v>
       </c>
       <c r="G3" t="n">
         <v>1.7363</v>
@@ -688,13 +688,13 @@
         <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0275</v>
+        <v>-0.0541</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4193</v>
+        <v>0.2138</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3918</v>
+        <v>-0.2679</v>
       </c>
       <c r="V3" t="n">
         <v>3.8113</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2329</v>
+        <v>4.2159</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9449</v>
+        <v>4.1757</v>
       </c>
       <c r="F4" t="n">
-        <v>0.288</v>
+        <v>0.0402</v>
       </c>
       <c r="G4" t="n">
         <v>1.7298</v>
@@ -766,13 +766,13 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5581</v>
+        <v>0.5411</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5928</v>
+        <v>0.8235</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0347</v>
+        <v>-0.2824</v>
       </c>
       <c r="V4" t="n">
         <v>1.5785</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5777</v>
+        <v>2.3164</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0589</v>
+        <v>2.0989</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4812</v>
+        <v>0.2174</v>
       </c>
       <c r="G5" t="n">
-        <v>1.039</v>
+        <v>1.1674</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4012</v>
+        <v>0.8467</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6378</v>
+        <v>0.3207</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5733</v>
+        <v>2.6223</v>
       </c>
       <c r="K5" t="n">
-        <v>1.198</v>
+        <v>1.8206</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3753</v>
+        <v>0.8017</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5342</v>
+        <v>-1.4549</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7968</v>
+        <v>-0.9739</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.481</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8502</v>
+        <v>0.1148</v>
       </c>
       <c r="T5" t="n">
-        <v>1.08</v>
+        <v>0.5762</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2297</v>
+        <v>-0.4614</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3219</v>
+        <v>0.3011</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0387</v>
+        <v>2.2414</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7965</v>
+        <v>0.6918</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2422</v>
+        <v>1.5496</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1674</v>
+        <v>3.0658</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8467</v>
+        <v>-1.0183</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3207</v>
+        <v>4.0841</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6223</v>
+        <v>2.4694</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8206</v>
+        <v>-0.9418</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8017</v>
+        <v>3.4112</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4549</v>
+        <v>0.5964</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9739</v>
+        <v>-0.0765</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.481</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0995</v>
+        <v>-2.0158</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8326</v>
+        <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1628</v>
+        <v>-0.4291</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2738</v>
+        <v>-0.0837</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4366</v>
+        <v>-0.3454</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3011</v>
+        <v>-0.945</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3011</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8255</v>
+        <v>2.1491</v>
       </c>
       <c r="E7" t="n">
-        <v>1.85</v>
+        <v>2.7293</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0245</v>
+        <v>-0.5803</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6619</v>
+        <v>1.039</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7549</v>
+        <v>0.4012</v>
       </c>
       <c r="I7" t="n">
-        <v>0.907</v>
+        <v>0.6378</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0423</v>
+        <v>2.5733</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1671</v>
+        <v>1.198</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8752</v>
+        <v>1.3753</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3804</v>
+        <v>-1.5342</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4122</v>
+        <v>-0.7968</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0318</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6977</v>
+        <v>0.4216</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0905</v>
+        <v>0.7504</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7882</v>
+        <v>-0.3288</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3115</v>
+        <v>0.3219</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5434</v>
+        <v>1.9193</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1053</v>
+        <v>1.919</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6487</v>
+        <v>0.0003</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0658</v>
+        <v>1.6619</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0183</v>
+        <v>0.7549</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0841</v>
+        <v>0.907</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4694</v>
+        <v>2.0423</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9418</v>
+        <v>1.1671</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4112</v>
+        <v>0.8752</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5964</v>
+        <v>-0.3804</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0765</v>
+        <v>-0.4122</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.0318</v>
       </c>
       <c r="P8" t="n">
         <v>0.5498</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5656</v>
+        <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1272</v>
+        <v>-0.6039</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8808</v>
+        <v>0.1595</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2463</v>
+        <v>-0.7634</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.945</v>
+        <v>0.3115</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3219</v>
+        <v>0.6335</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. HATHOUTI LAHRECH</t>
+          <t>Q. GJENERALI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8568</v>
+        <v>1.5087</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2478</v>
+        <v>0.1376</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1046</v>
+        <v>1.3712</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5619</v>
+        <v>4.8412</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1356</v>
+        <v>4.7643</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4263</v>
+        <v>0.077</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1376</v>
+        <v>3.9547</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0959</v>
+        <v>4.4866</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0417</v>
+        <v>-0.5319</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4243</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0397</v>
+        <v>0.2777</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3846</v>
+        <v>0.6089</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5498</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8447</v>
+        <v>-0.5445</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5309</v>
+        <v>-0.152</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3138</v>
+        <v>-0.3925</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7693</v>
+        <v>0.9126</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8445</v>
+        <v>0.9135</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0752</v>
+        <v>-0.0009</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6362</v>
@@ -1234,13 +1234,13 @@
         <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4892</v>
+        <v>0.6325</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8047</v>
+        <v>0.8737</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3155</v>
+        <v>-0.2412</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q. GJENERALI</t>
+          <t>S. HATHOUTI LAHRECH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7633</v>
+        <v>0.4474</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.261</v>
+        <v>-0.6324</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0243</v>
+        <v>1.0798</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8412</v>
+        <v>0.5619</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7643</v>
+        <v>0.1356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.077</v>
+        <v>0.4263</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9547</v>
+        <v>0.1376</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4866</v>
+        <v>0.0959</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5319</v>
+        <v>0.0417</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.4243</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2777</v>
+        <v>0.0397</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6089</v>
+        <v>0.3846</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8326</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2899</v>
+        <v>0.4353</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5505</v>
+        <v>0.1463</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.289</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6007</v>
+        <v>-2.1417</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2555</v>
+        <v>-0.8709</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3452</v>
+        <v>-1.2709</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8885</v>
@@ -1468,13 +1468,13 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6284</v>
+        <v>-0.1695</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1652</v>
+        <v>0.2195</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4633</v>
+        <v>-0.389</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.3938</v>
+        <v>29.7701</v>
       </c>
       <c r="E14" t="n">
-        <v>21.91699999999999</v>
+        <v>23.2933</v>
       </c>
       <c r="F14" t="n">
-        <v>6.476800000000001</v>
+        <v>6.4767</v>
       </c>
       <c r="G14" t="n">
         <v>20.08</v>
       </c>
       <c r="H14" t="n">
-        <v>9.020399999999999</v>
+        <v>9.0204</v>
       </c>
       <c r="I14" t="n">
         <v>11.0596</v>
@@ -1531,10 +1531,10 @@
         <v>-5.330299999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.0074</v>
+        <v>-5.007400000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3227999999999999</v>
+        <v>-0.3227999999999998</v>
       </c>
       <c r="P14" t="n">
         <v>4.581399999999999</v>
@@ -1546,10 +1546,10 @@
         <v>19.2421</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0032</v>
+        <v>0.3732</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2777</v>
+        <v>3.6539</v>
       </c>
       <c r="U14" t="n">
         <v>-3.2807</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.1395</v>
+        <v>6.4013</v>
       </c>
       <c r="E15" t="n">
-        <v>9.793699999999999</v>
+        <v>8.4475</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6542</v>
+        <v>-2.0462</v>
       </c>
       <c r="G15" t="n">
         <v>4.8656</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4571</v>
+        <v>0.7189</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0679</v>
+        <v>0.7217</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3892</v>
+        <v>-0.0028</v>
       </c>
       <c r="V15" t="n">
         <v>0.6335</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0386</v>
+        <v>0.4699</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8158</v>
+        <v>1.2004</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.7304</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1966</v>
@@ -1702,13 +1702,13 @@
         <v>0.3665</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1927</v>
+        <v>0.3158</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2572</v>
+        <v>0.1275</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0645</v>
+        <v>0.1883</v>
       </c>
       <c r="V16" t="n">
         <v>1.267</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6884</v>
+        <v>-1.2295</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.328</v>
+        <v>0.0567</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3605</v>
+        <v>-1.2862</v>
       </c>
       <c r="G17" t="n">
         <v>-1.324</v>
@@ -1780,13 +1780,13 @@
         <v>0.733</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7755</v>
+        <v>-0.3165</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4404</v>
+        <v>-0.0558</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3351</v>
+        <v>-0.2608</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3219</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0083</v>
+        <v>-1.6674</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0069</v>
+        <v>-0.8146</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0014</v>
+        <v>-0.8527</v>
       </c>
       <c r="G18" t="n">
         <v>-2.6481</v>
@@ -1858,13 +1858,13 @@
         <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4152</v>
+        <v>-0.0743</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1304</v>
+        <v>0.0619</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2848</v>
+        <v>-0.1361</v>
       </c>
       <c r="V18" t="n">
         <v>0.3219</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0333</v>
+        <v>-2.7734</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0301</v>
+        <v>-0.7994</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0031</v>
+        <v>-1.974</v>
       </c>
       <c r="G19" t="n">
         <v>-2.048</v>
@@ -1936,13 +1936,13 @@
         <v>0.733</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4362</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>1.684</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2478</v>
+        <v>-0.2187</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3219</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.7753</v>
+        <v>-4.4795</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4828</v>
+        <v>-2.2905</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2924</v>
+        <v>-2.189</v>
       </c>
       <c r="G20" t="n">
         <v>-4.5936</v>
@@ -2014,13 +2014,13 @@
         <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0016</v>
+        <v>0.2973</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3281</v>
+        <v>0.5204</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3265</v>
+        <v>-0.2231</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. MARI LOPEZ-ROCA</t>
+          <t>R. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0748</v>
+        <v>-5.3931</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0789</v>
+        <v>-2.0752</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.1537</v>
+        <v>-3.3179</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.929</v>
+        <v>-1.522</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8232</v>
+        <v>0.9721</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1058</v>
+        <v>-2.4941</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3729</v>
+        <v>1.8258</v>
       </c>
       <c r="K21" t="n">
-        <v>0.978</v>
+        <v>2.9412</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3949</v>
+        <v>-1.1154</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.302</v>
+        <v>-3.3478</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8012</v>
+        <v>-1.9691</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.5008</v>
+        <v>-1.3787</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.8484</v>
+        <v>-3.1154</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0158</v>
+        <v>2.1991</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2208</v>
+        <v>-0.1197</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5543</v>
+        <v>0.149</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3336</v>
+        <v>-0.2687</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.5339</v>
+        <v>-2.8351</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.9346</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5339</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. CARRION BALLESTER</t>
+          <t>H. MARI LOPEZ-ROCA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.4115</v>
+        <v>-5.6735</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9406</v>
+        <v>-0.5942</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4709</v>
+        <v>-5.0793</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.522</v>
+        <v>-1.929</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9721</v>
+        <v>-0.8232</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4941</v>
+        <v>-1.1058</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8258</v>
+        <v>2.3729</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9412</v>
+        <v>0.978</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1154</v>
+        <v>1.3949</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3478</v>
+        <v>-4.302</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.9691</v>
+        <v>-1.8012</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3787</v>
+        <v>-2.5008</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1154</v>
+        <v>-3.8484</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1991</v>
+        <v>2.0158</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1381</v>
+        <v>0.622</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7164</v>
+        <v>0.8813</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4217</v>
+        <v>-0.2593</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.8351</v>
+        <v>-2.5339</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.9346</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.9005</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6459</v>
+        <v>-5.9917</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.2068</v>
+        <v>-5.7261</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.439</v>
+        <v>-0.2656</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2215</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2411</v>
+        <v>-0.5869</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8258</v>
+        <v>-0.345</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4153</v>
+        <v>-0.2419</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.8574</v>
+        <v>-7.416</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4368</v>
+        <v>-5.1483</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4206</v>
+        <v>-2.2676</v>
       </c>
       <c r="G24" t="n">
         <v>-5.4628</v>
@@ -2326,13 +2326,13 @@
         <v>2.0158</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.35</v>
+        <v>0.0914</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0166</v>
+        <v>0.3051</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3666</v>
+        <v>-0.2136</v>
       </c>
       <c r="V24" t="n">
         <v>-0.945</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-28.394</v>
+        <v>-27.7529</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.743600000000001</v>
+        <v>-7.743699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-20.6501</v>
+        <v>-20.0089</v>
       </c>
       <c r="G25" t="n">
         <v>-20.08</v>
@@ -2404,13 +2404,13 @@
         <v>14.6605</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0031</v>
+        <v>1.6441</v>
       </c>
       <c r="T25" t="n">
-        <v>3.280699999999999</v>
+        <v>3.2809</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.2777</v>
+        <v>-1.6367</v>
       </c>
       <c r="V25" t="n">
         <v>-4.7354</v>
